--- a/site/tournage.xlsx
+++ b/site/tournage.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Gerer les freins et innover comme apprentissage</t>
+          <t>Innover comme processus d'apprentissage</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Temps, légitimité, entourage, doute ; incertitude, essais, pivot ; première action reversible.</t>
+          <t>Incertitude, essais, erreurs, pivot et progression plutot que reussite lineaire ; leviers existants pour depasser les freins.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Gerer les freins et innover comme apprentissage</t>
+          <t>Innover comme processus d'apprentissage</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Temps, légitimité, entourage, doute ; incertitude, essais, pivot ; première action reversible.</t>
+          <t>Incertitude, essais, erreurs, pivot et progression plutot que reussite lineaire ; leviers existants pour depasser les freins.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
